--- a/order_forms/038_culinary_knife_sharpening_service_order_form--order_forms.xlsx
+++ b/order_forms/038_culinary_knife_sharpening_service_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'alice'}</t>
+          <t>alice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Alice'}</t>
+          <t>Alice</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"chef's_knife"}</t>
+          <t>chef's_knife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "Chef's Knife"}</t>
+          <t>Chef's Knife</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'paring_knife'}</t>
+          <t>paring_knife</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Paring Knife'}</t>
+          <t>Paring Knife</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'utility_knife'}</t>
+          <t>utility_knife</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Utility Knife'}</t>
+          <t>Utility Knife</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'delux'}</t>
+          <t>delux</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Delux'}</t>
+          <t>Delux</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
